--- a/review/abilities/workbooks/23_Class_Leader.xlsx
+++ b/review/abilities/workbooks/23_Class_Leader.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Level 1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Level 3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Level 7" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="All Signatures" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Balance Check" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Power Watchlist" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Change Log" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level 1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level 3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level 7" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Signatures" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Check" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Power Watchlist" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Level 1'!$A$4:$M$7</definedName>
@@ -27,9 +27,9 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'All Signatures'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Power Watchlist'!$A$4:$J$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Power Watchlist'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Change Log'!$A$4:$R$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Change Log'!$A$4:$Q$204</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Change Log'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'Change Log'!$A$1:$R$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'Change Log'!$A$1:$Q$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -183,7 +183,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="4">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -220,19 +220,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00F8CBAD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <b val="1"/>
-        <color rgb="001F3864"/>
-        <sz val="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00D9E1F2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1003,8 +990,8 @@
   </sheetData>
   <mergeCells count="31">
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="B11:D11"/>
-    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="A20:D20"/>
@@ -1173,7 +1160,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -1183,32 +1170,32 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
+          <t>Aid two allies for one Aid action; each gains 1 Boon to its next matching roll.</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
           <t>When you use Aid, you may assist two allies instead of one. Name the task for each and explain how your signal helps. Each gains Aid’s normal 1 Boon to its next matching roll before the start of your next turn. Outside combat, Aid still replaces your own contribution to a group roll.</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>When you use Aid, you may assist two allies instead of one. Name the task for each and explain how your signal helps. Each gains Aid’s normal 1 Boon to its next matching roll before the start of your next turn. Outside combat, Aid still replaces your own contribution to a group roll.</t>
-        </is>
-      </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Aid two allies for one Maneuver; excellent action compression and likely the default level-1 pick.</t>
+          <t>Aid two allies for one action; excellent action compression and a strong level 1 anchor.</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>Strong. Consider whether the other level-1 options compete; clarify whether both allies must be within 3 squares of you or of each other.</t>
+          <t>Approved: one two-recipient Aid on your turn; each ally within 3 squares of you and able to see or hear the signal.</t>
         </is>
       </c>
       <c r="J5" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>Power spike</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr"/>
@@ -1222,52 +1209,52 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>signature-leader-lead-the-step</t>
+          <t>Lead the Way</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Passive</t>
+          <t>Maneuver</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Up to two adjacent willing allies, when you use Disengage.</t>
+          <t>Self; any willing allies within 3 squares who can see or hear you.</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Each chosen ally may move 1 square without provoking, in an order you choose. Your Disengage works normally. The allies spend no actions or movement allowances and must end in separate free squares.</t>
+          <t>Move using your Speed; allies within 3 may follow up to the distance moved, maximum 2 squares. Allies who come within 3 during the move can join.</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Each chosen ally may move 1 square without provoking, in an order you choose. Your Disengage works normally. The allies spend no actions or movement allowances and must end in separate free squares.</t>
+          <t>When you move using your Speed, any willing ally within 3 squares who can see or hear you may move with you at the same time, following your path, up to the distance you move, to a maximum of 2 squares. An ally who comes within 3 squares during your movement may join for the remainder of that movement. The allies spend no movement. This movement follows normal opportunity attack rules.</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Disengage grants two allies a 1-square move; good withdrawal and formation tool.</t>
+          <t>Lead the Way: Maneuver formation move. Allies within 3 follow up to 2 squares, and allies who come within 3 during the move can join for the remainder. Strong distinct party mobility.</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Clarify whether the allies move before or after your Disengage and whether they can end adjacent to enemies.</t>
+          <t>Approved: Maneuver; move using Speed; willing allies within 3 who see or hear follow up to the distance moved, maximum 2 squares; dynamic pickup; no movement cost; normal opportunity attacks; once per turn.</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L6" s="8" t="inlineStr"/>
@@ -1291,7 +1278,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -1301,32 +1288,32 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Both gain 1 Boon to defense until the start of your next turn while adjacent to one another. You must remain able to act. Reusing this card replaces your previous application; it does not multiply it.</t>
+          <t>Self and one adjacent ally each gain 2 Boons to defense while adjacent until the start of your next turn.</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Both gain 1 Boon to defense until the start of your next turn while adjacent to one another. You must remain able to act. Reusing this card replaces your previous application; it does not multiply it.</t>
+          <t>You and one adjacent willing ally each gain 2 Boons to defense until the start of your next turn while you remain adjacent.</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Self and one ally gain 1 Boon to defense while adjacent; solid paired defense.</t>
+          <t>Paired defensive stance: self and one adjacent ally gain 2 Boons to defense while adjacent. Strong level 1 defensive option.</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Clarify whether the Boon applies to all defenses or one, and whether it ends immediately if adjacency is lost (text says yes).</t>
+          <t>Approved: Maneuver; self and one adjacent willing ally gain 2 Boons to defense until the start of the next turn while adjacent.</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr"/>
@@ -1349,15 +1336,12 @@
       <formula>L5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>L5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>L5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -1489,52 +1473,52 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>signature-leader-hold-your-nerve</t>
+          <t>Blow the Horn</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Reaction</t>
+          <t>Maneuver</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Guile</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>One willing ally within 4 squares that can hear you, when it gains temporary Frightened or Dazed.</t>
+          <t>Every enemy within 5 squares that can hear you.</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Reduce the newly applied contribution of that condition by up to 2, minimum 0, before it takes effect. This does not remove an older contribution or a starred source. No HP is restored.</t>
+          <t>One Guile roll against all enemies in range. Weak Frightened 1; Standard Frightened 1 and Dazed 1; Strong Frightened 2 and Dazed 1.</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Reduce the newly applied contribution of that condition by up to 2, minimum 0, before it takes effect. This does not remove an older contribution or a starred source. No HP is restored.</t>
+          <t>Make one Guile roll and apply the result to each target. On a Weak result, apply Frightened 1. On a Standard result, apply Frightened 1 and Dazed 1. On a Strong result, apply Frightened 2 and Dazed 1.</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Reaction to reduce a newly applied Frightened or Dazed contribution by 2; narrow but strong against those conditions.</t>
+          <t>Blow the Horn: Maneuver Guile roll against every enemy within 5 that can hear; Weak Frightened 1, Standard Frightened 1 and Dazed 1, Strong Frightened 2 and Dazed 1. Strong area control.</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>Clarify 'newly applied contribution' versus an existing condition and add an example. Consider widening to Bleeding or Poisoned if it feels too narrow.</t>
+          <t>Approved: Maneuver, Guile, one roll for all enemies within 5 that can hear, Weak Frightened 1, Standard Frightened 1 and Dazed 1, Strong Frightened 2 and Dazed 1.</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr"/>
@@ -1548,52 +1532,55 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>signature-leader-orderly-withdrawal</t>
+          <t>Lead by Example</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Maneuver</t>
+          <t>Main Action</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Guile</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Two willing allies within 4 squares that can perceive your signal.</t>
+          <t>One creature within reach of your melee weapon.</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Each may move up to 2 squares without provoking, in an order you choose. Each may end farther from or nearer to the fight as needed; no attack is granted. Choose legal routes and free endpoints.</t>
+          <t>Guile melee attack for 2/4/6 physical damage. Standard chooses one control effect; Strong chooses two: Dazed 1, ally move 1, or ally attack Boon.</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Each may move up to 2 squares without provoking, in an order you choose. Each may end farther from or nearer to the fight as needed; no attack is granted. Choose legal routes and free endpoints.</t>
+          <t>Make a melee weapon attack using Guile instead of Brawn. On a Weak result, deal 2 physical damage. On a Standard result, deal 4 physical damage and choose one effect. On a Strong result, deal 6 physical damage and choose two different effects.
+- Break Their Guard: The target gains Dazed 1.
+- Open the Line: Each ally within 5 squares who can see or hear you may move 1 square without provoking.
+- Point the Way: Each ally within 5 squares who can see or hear you gains 1 Boon to their next attack against the target.</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Two allies move 2 without provoking; strong disengage and formation reset.</t>
+          <t>Lead by Example: Guile melee attack for 2/4/6 physical damage. Standard chooses one control effect, Strong chooses two: Dazed 1, ally move 1, or ally Boon against the target. Strong battlefield control.</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Clarify whether the allies can move in different directions and whether they must remain within signal range.</t>
+          <t>Approved: Main Action, Guile melee weapon attack, 2/4/6 physical damage, Standard one effect, Strong two different effects, Dazed 1 / ally move 1 / ally attack Boon.</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L6" s="8" t="inlineStr"/>
@@ -1617,7 +1604,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -1627,12 +1614,12 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>The ally makes one free Basic Melee attack against an adjacent enemy, using its own Brawn and Basic Melee outcomes. On Strong, it may also push the target 1 square directly away from itself. The ally needs a melee weapon and must be able to attack. Free attacks trigger no further free attacks.</t>
+          <t>Ally makes one free Basic Melee attack against an adjacent enemy and may push the target 1 on a Strong result.</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>The ally makes one free Basic Melee attack against an adjacent enemy, using its own Brawn and Basic Melee outcomes. On Strong, it may also push the target 1 square directly away from itself. The ally needs a melee weapon and must be able to attack. Free attacks trigger no further free attacks.</t>
+          <t>The ally makes one free Basic Melee attack against an adjacent enemy. On a Strong result, the ally may also push the target 1. This requires a melee weapon and the ability to attack. This is a single free Basic Melee attack.</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
@@ -1642,17 +1629,17 @@
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Compare to shared 'grant an attack' cards; monitor. Clarify that the ally uses its own weapon and that no chains occur.</t>
+          <t>Approved: lean wording. The ally makes one free Basic Melee attack and may push the target 1 on a Strong result; this is a single free attack.</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr"/>
@@ -1675,15 +1662,12 @@
       <formula>L5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>L5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>L5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -1825,7 +1809,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -1835,12 +1819,12 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Each ally may move up to 3 squares without provoking, then make one free Basic Melee attack against an adjacent enemy if able. Resolve one ally completely before the other. Each attack uses that ally’s Brawn and Basic Melee outcomes; on Strong it may push its target 1 square. Weapons are required.</t>
+          <t>Two allies move 3 without provoking, then each makes a free Basic Melee; push 1 on Strong.</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Each ally may move up to 3 squares without provoking, then make one free Basic Melee attack against an adjacent enemy if able. Resolve one ally completely before the other. Each attack uses that ally’s Brawn and Basic Melee outcomes; on Strong it may push its target 1 square. Weapons are required. These attacks trigger no further free attacks.</t>
+          <t>Each ally may move up to 3 squares without provoking, then make one free Basic Melee attack against an adjacent enemy if able. Resolve one ally completely before the other. On a Strong result, the attack may push its target 1.</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
@@ -1850,17 +1834,17 @@
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>Very strong; monitor. The text already says each ally uses its own Brawn and that no chains occur; keep that visible in play.</t>
+          <t>Approved: two allies move 3 and make one free Basic Melee each; push 1 on Strong. Lean wording, no extra weapon or chain text.</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr"/>
@@ -1884,7 +1868,7 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
@@ -1894,32 +1878,32 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Each recipient reduces temporary Frightened by up to 2, minimum 0, and gains 1 Boon to its next defense before the start of your next turn. Each may immediately move 1 square without provoking. Resolve movement in an order you choose. No effect on starred conditions, and no restoration of actions already spent.</t>
+          <t>Self and up to three allies reduce one Frightened or Dazed condition by 2, gain a defense Boon, and move 1 without provoking.</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Each recipient reduces temporary Frightened by up to 2, minimum 0, and gains 1 Boon to its next defense before the start of your next turn. Each may immediately move 1 square without provoking. Resolve movement in an order you choose. No effect on starred conditions, and no restoration of actions already spent.</t>
+          <t>Each recipient reduces one Frightened or Dazed condition by up to 2, to a minimum of 0, and gains 1 Boon to its next defense before the start of your next turn. Each may immediately move 1 square without provoking. Resolve movement in an order you choose. This applies to ordinary conditions.</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Four recipients reduce Frightened by 2, gain a defense Boon and move 1; strong fear recovery.</t>
+          <t>Party anti-rout: four recipients reduce one Frightened or Dazed condition by 2, gain a defense Boon and move 1. Strong Master recovery.</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Very strong in fear-heavy campaigns. Consider three recipients or removing the movement if it dominates; clarify that it cannot touch starred fear.</t>
+          <t>Approved: Maneuver; self plus three allies within 4; reduce one Frightened or Dazed condition by 2; defense Boon; move 1 without provoking; ordinary conditions only.</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L6" s="8" t="inlineStr"/>
@@ -1943,7 +1927,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -1953,32 +1937,32 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Grant 2 Boons to that defense. After the entire attack resolves, the ally may move up to 3 squares without provoking if still able. This does not invalidate, redirect or rewind the attack.</t>
+          <t>Grant 2 Boons to an ally defense, then the ally may move up to 3 squares without provoking after the attack.</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Grant 2 Boons to that defense. After the entire attack resolves, the ally may move up to 3 squares without provoking if still able. This does not invalidate, redirect or rewind the attack.</t>
+          <t>Grant 2 Boons to that defense. After the entire attack resolves, the ally may move up to 3 squares without provoking if still able.</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Reaction granting 2 Boons to an ally's defense and a 3-square move; strong Master protection.</t>
+          <t>Reaction granting 2 Boons to an ally defense and a 3-square move; strong Master protection.</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>2 Boons plus movement on a Reaction is powerful. Playtest; consider 1 Boon or a shorter move. Clarify whether a Dying or immobilized ally can move.</t>
+          <t>Approved: 2 Boons to the defense and up to 3 squares of movement after the attack if able. Clean wording only.</t>
         </is>
       </c>
       <c r="J7" s="9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>Power spike</t>
+          <t>None</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr"/>
@@ -2001,15 +1985,12 @@
       <formula>L5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>L5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>L5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="L5:L7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -2156,7 +2137,7 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -2166,17 +2147,17 @@
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>When you use Aid, you may assist two allies instead of one. Name the task for each and explain how your signal helps. Each gains Aid’s normal 1 Boon to its next matching roll before the start of your next turn. Outside combat, Aid still replaces your own contribution to a group roll.</t>
+          <t>Aid two allies for one Aid action; each gains 1 Boon to its next matching roll.</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Aid two allies for one Maneuver; excellent action compression and likely the default level-1 pick.</t>
+          <t>Aid two allies for one action; excellent action compression and a strong level 1 anchor.</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>Strong. Consider whether the other level-1 options compete; clarify whether both allies must be within 3 squares of you or of each other.</t>
+          <t>Approved: one two-recipient Aid on your turn; each ally within 3 squares of you and able to see or hear the signal.</t>
         </is>
       </c>
       <c r="J5" s="9" t="inlineStr">
@@ -2200,7 +2181,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Lead the Step</t>
+          <t>Lead the Way</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -2210,32 +2191,32 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Passive</t>
+          <t>Maneuver</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Up to two adjacent willing allies, when you use Disengage.</t>
+          <t>Self; any willing allies within 3 squares who can see or hear you.</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Each chosen ally may move 1 square without provoking, in an order you choose. Your Disengage works normally. The allies spend no actions or movement allowances and must end in separate free squares.</t>
+          <t>Move using your Speed; allies within 3 may follow up to the distance moved, maximum 2 squares. Allies who come within 3 during the move can join.</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Disengage grants two allies a 1-square move; good withdrawal and formation tool.</t>
+          <t>Lead the Way: Maneuver formation move. Allies within 3 follow up to 2 squares, and allies who come within 3 during the move can join for the remainder. Strong distinct party mobility.</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Clarify whether the allies move before or after your Disengage and whether they can end adjacent to enemies.</t>
+          <t>Approved: Maneuver; move using Speed; willing allies within 3 who see or hear follow up to the distance moved, maximum 2 squares; dynamic pickup; no movement cost; normal opportunity attacks; once per turn.</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -2274,7 +2255,7 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -2284,17 +2265,17 @@
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Both gain 1 Boon to defense until the start of your next turn while adjacent to one another. You must remain able to act. Reusing this card replaces your previous application; it does not multiply it.</t>
+          <t>Self and one adjacent ally each gain 2 Boons to defense while adjacent until the start of your next turn.</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Self and one ally gain 1 Boon to defense while adjacent; solid paired defense.</t>
+          <t>Paired defensive stance: self and one adjacent ally gain 2 Boons to defense while adjacent. Strong level 1 defensive option.</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Clarify whether the Boon applies to all defenses or one, and whether it ends immediately if adjacency is lost (text says yes).</t>
+          <t>Approved: Maneuver; self and one adjacent willing ally gain 2 Boons to defense until the start of the next turn while adjacent.</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
@@ -2318,7 +2299,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Hold Your Nerve</t>
+          <t>Blow the Horn</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -2328,32 +2309,32 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Reaction</t>
+          <t>Maneuver</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Guile</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>One willing ally within 4 squares that can hear you, when it gains temporary Frightened or Dazed.</t>
+          <t>Every enemy within 5 squares that can hear you.</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>Reduce the newly applied contribution of that condition by up to 2, minimum 0, before it takes effect. This does not remove an older contribution or a starred source. No HP is restored.</t>
+          <t>One Guile roll against all enemies in range. Weak Frightened 1; Standard Frightened 1 and Dazed 1; Strong Frightened 2 and Dazed 1.</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>Reaction to reduce a newly applied Frightened or Dazed contribution by 2; narrow but strong against those conditions.</t>
+          <t>Blow the Horn: Maneuver Guile roll against every enemy within 5 that can hear; Weak Frightened 1, Standard Frightened 1 and Dazed 1, Strong Frightened 2 and Dazed 1. Strong area control.</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>Clarify 'newly applied contribution' versus an existing condition and add an example. Consider widening to Bleeding or Poisoned if it feels too narrow.</t>
+          <t>Approved: Maneuver, Guile, one roll for all enemies within 5 that can hear, Weak Frightened 1, Standard Frightened 1 and Dazed 1, Strong Frightened 2 and Dazed 1.</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
@@ -2377,7 +2358,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Orderly Withdrawal</t>
+          <t>Lead by Example</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -2387,32 +2368,32 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Maneuver</t>
+          <t>Main Action</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>Guile</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>Two willing allies within 4 squares that can perceive your signal.</t>
+          <t>One creature within reach of your melee weapon.</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Each may move up to 2 squares without provoking, in an order you choose. Each may end farther from or nearer to the fight as needed; no attack is granted. Choose legal routes and free endpoints.</t>
+          <t>Guile melee attack for 2/4/6 physical damage. Standard chooses one control effect; Strong chooses two: Dazed 1, ally move 1, or ally attack Boon.</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>Two allies move 2 without provoking; strong disengage and formation reset.</t>
+          <t>Lead by Example: Guile melee attack for 2/4/6 physical damage. Standard chooses one control effect, Strong chooses two: Dazed 1, ally move 1, or ally Boon against the target. Strong battlefield control.</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>Clarify whether the allies can move in different directions and whether they must remain within signal range.</t>
+          <t>Approved: Main Action, Guile melee weapon attack, 2/4/6 physical damage, Standard one effect, Strong two different effects, Dazed 1 / ally move 1 / ally attack Boon.</t>
         </is>
       </c>
       <c r="J9" s="7" t="inlineStr">
@@ -2451,7 +2432,7 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
@@ -2461,7 +2442,7 @@
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>The ally makes one free Basic Melee attack against an adjacent enemy, using its own Brawn and Basic Melee outcomes. On Strong, it may also push the target 1 square directly away from itself. The ally needs a melee weapon and must be able to attack. Free attacks trigger no further free attacks.</t>
+          <t>Ally makes one free Basic Melee attack against an adjacent enemy and may push the target 1 on a Strong result.</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
@@ -2471,7 +2452,7 @@
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>Compare to shared 'grant an attack' cards; monitor. Clarify that the ally uses its own weapon and that no chains occur.</t>
+          <t>Approved: lean wording. The ally makes one free Basic Melee attack and may push the target 1 on a Strong result; this is a single free attack.</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
@@ -2510,7 +2491,7 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -2520,7 +2501,7 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Each ally may move up to 3 squares without provoking, then make one free Basic Melee attack against an adjacent enemy if able. Resolve one ally completely before the other. Each attack uses that ally’s Brawn and Basic Melee outcomes; on Strong it may push its target 1 square. Weapons are required.</t>
+          <t>Two allies move 3 without provoking, then each makes a free Basic Melee; push 1 on Strong.</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -2530,7 +2511,7 @@
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>Very strong; monitor. The text already says each ally uses its own Brawn and that no chains occur; keep that visible in play.</t>
+          <t>Approved: two allies move 3 and make one free Basic Melee each; push 1 on Strong. Lean wording, no extra weapon or chain text.</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr">
@@ -2569,7 +2550,7 @@
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -2579,17 +2560,17 @@
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>Each recipient reduces temporary Frightened by up to 2, minimum 0, and gains 1 Boon to its next defense before the start of your next turn. Each may immediately move 1 square without provoking. Resolve movement in an order you choose. No effect on starred conditions, and no restoration of actions already spent.</t>
+          <t>Self and up to three allies reduce one Frightened or Dazed condition by 2, gain a defense Boon, and move 1 without provoking.</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>Four recipients reduce Frightened by 2, gain a defense Boon and move 1; strong fear recovery.</t>
+          <t>Party anti-rout: four recipients reduce one Frightened or Dazed condition by 2, gain a defense Boon and move 1. Strong Master recovery.</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>Very strong in fear-heavy campaigns. Consider three recipients or removing the movement if it dominates; clarify that it cannot touch starred fear.</t>
+          <t>Approved: Maneuver; self plus three allies within 4; reduce one Frightened or Dazed condition by 2; defense Boon; move 1 without provoking; ordinary conditions only.</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
@@ -2628,7 +2609,7 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>None — no roll</t>
+          <t>None (no roll)</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -2638,17 +2619,17 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Grant 2 Boons to that defense. After the entire attack resolves, the ally may move up to 3 squares without provoking if still able. This does not invalidate, redirect or rewind the attack.</t>
+          <t>Grant 2 Boons to an ally defense, then the ally may move up to 3 squares without provoking after the attack.</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>Reaction granting 2 Boons to an ally's defense and a 3-square move; strong Master protection.</t>
+          <t>Reaction granting 2 Boons to an ally defense and a 3-square move; strong Master protection.</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>2 Boons plus movement on a Reaction is powerful. Playtest; consider 1 Boon or a shorter move. Clarify whether a Dying or immobilized ally can move.</t>
+          <t>Approved: 2 Boons to the defense and up to 3 squares of movement after the attack if able. Clean wording only.</t>
         </is>
       </c>
       <c r="J13" s="9" t="inlineStr">
@@ -2681,15 +2662,12 @@
       <formula>L5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>L5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>L5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="L5:L13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -3293,15 +3271,12 @@
       <formula>H5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>H5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>H5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="H5:H6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -3325,7 +3300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3340,12 +3315,11 @@
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" style="10" min="17" max="17"/>
-    <col width="30" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" style="10" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -3426,30 +3400,25 @@
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
-          <t>Playtest status</t>
+          <t>Book issue</t>
         </is>
       </c>
       <c r="N4" s="6" t="inlineStr">
         <is>
-          <t>Book issue</t>
+          <t>Foundry issue</t>
         </is>
       </c>
       <c r="O4" s="6" t="inlineStr">
         <is>
-          <t>Foundry issue</t>
+          <t>Commit SHA</t>
         </is>
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>Commit SHA</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -3473,7 +3442,6 @@
       <c r="O5" s="7" t="inlineStr"/>
       <c r="P5" s="7" t="inlineStr"/>
       <c r="Q5" s="7" t="inlineStr"/>
-      <c r="R5" s="7" t="inlineStr"/>
     </row>
     <row r="6" ht="16.5" customHeight="1">
       <c r="A6" s="8" t="inlineStr"/>
@@ -3493,7 +3461,6 @@
       <c r="O6" s="8" t="inlineStr"/>
       <c r="P6" s="8" t="inlineStr"/>
       <c r="Q6" s="8" t="inlineStr"/>
-      <c r="R6" s="8" t="inlineStr"/>
     </row>
     <row r="7" ht="16.5" customHeight="1">
       <c r="A7" s="7" t="inlineStr"/>
@@ -3513,7 +3480,6 @@
       <c r="O7" s="7" t="inlineStr"/>
       <c r="P7" s="7" t="inlineStr"/>
       <c r="Q7" s="7" t="inlineStr"/>
-      <c r="R7" s="7" t="inlineStr"/>
     </row>
     <row r="8" ht="16.5" customHeight="1">
       <c r="A8" s="8" t="inlineStr"/>
@@ -3533,7 +3499,6 @@
       <c r="O8" s="8" t="inlineStr"/>
       <c r="P8" s="8" t="inlineStr"/>
       <c r="Q8" s="8" t="inlineStr"/>
-      <c r="R8" s="8" t="inlineStr"/>
     </row>
     <row r="9" ht="16.5" customHeight="1">
       <c r="A9" s="7" t="inlineStr"/>
@@ -3553,7 +3518,6 @@
       <c r="O9" s="7" t="inlineStr"/>
       <c r="P9" s="7" t="inlineStr"/>
       <c r="Q9" s="7" t="inlineStr"/>
-      <c r="R9" s="7" t="inlineStr"/>
     </row>
     <row r="10" ht="16.5" customHeight="1">
       <c r="A10" s="8" t="inlineStr"/>
@@ -3573,7 +3537,6 @@
       <c r="O10" s="8" t="inlineStr"/>
       <c r="P10" s="8" t="inlineStr"/>
       <c r="Q10" s="8" t="inlineStr"/>
-      <c r="R10" s="8" t="inlineStr"/>
     </row>
     <row r="11" ht="16.5" customHeight="1">
       <c r="A11" s="7" t="inlineStr"/>
@@ -3593,7 +3556,6 @@
       <c r="O11" s="7" t="inlineStr"/>
       <c r="P11" s="7" t="inlineStr"/>
       <c r="Q11" s="7" t="inlineStr"/>
-      <c r="R11" s="7" t="inlineStr"/>
     </row>
     <row r="12" ht="16.5" customHeight="1">
       <c r="A12" s="8" t="inlineStr"/>
@@ -3613,7 +3575,6 @@
       <c r="O12" s="8" t="inlineStr"/>
       <c r="P12" s="8" t="inlineStr"/>
       <c r="Q12" s="8" t="inlineStr"/>
-      <c r="R12" s="8" t="inlineStr"/>
     </row>
     <row r="13" ht="16.5" customHeight="1">
       <c r="A13" s="7" t="inlineStr"/>
@@ -3633,7 +3594,6 @@
       <c r="O13" s="7" t="inlineStr"/>
       <c r="P13" s="7" t="inlineStr"/>
       <c r="Q13" s="7" t="inlineStr"/>
-      <c r="R13" s="7" t="inlineStr"/>
     </row>
     <row r="14" ht="16.5" customHeight="1">
       <c r="A14" s="8" t="inlineStr"/>
@@ -3653,7 +3613,6 @@
       <c r="O14" s="8" t="inlineStr"/>
       <c r="P14" s="8" t="inlineStr"/>
       <c r="Q14" s="8" t="inlineStr"/>
-      <c r="R14" s="8" t="inlineStr"/>
     </row>
     <row r="15" ht="16.5" customHeight="1">
       <c r="A15" s="7" t="inlineStr"/>
@@ -3673,7 +3632,6 @@
       <c r="O15" s="7" t="inlineStr"/>
       <c r="P15" s="7" t="inlineStr"/>
       <c r="Q15" s="7" t="inlineStr"/>
-      <c r="R15" s="7" t="inlineStr"/>
     </row>
     <row r="16" ht="16.5" customHeight="1">
       <c r="A16" s="8" t="inlineStr"/>
@@ -3693,23 +3651,19 @@
       <c r="O16" s="8" t="inlineStr"/>
       <c r="P16" s="8" t="inlineStr"/>
       <c r="Q16" s="8" t="inlineStr"/>
-      <c r="R16" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:R204"/>
+  <autoFilter ref="A4:Q204"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:R2"/>
-    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="2">
     <dataValidation sqref="I5:I204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Change type" error="Choose one of: Editorial, Wording, Mechanical, Rename, Add, Remove, Tier / DP, ID migration" promptTitle="Change type" prompt="Classify the change." type="list">
       <formula1>"Editorial,Wording,Mechanical,Rename,Add,Remove,Tier / DP,ID migration"</formula1>
     </dataValidation>
     <dataValidation sqref="K5:K204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose one of: Proposed, Approved, Rejected, Deferred" promptTitle="Decision" prompt="Approval state for this change." type="list">
       <formula1>"Proposed,Approved,Rejected,Deferred"</formula1>
-    </dataValidation>
-    <dataValidation sqref="M5:M204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Playtest status" error="Choose one of: Not needed, Pending, Passed, Failed, N/A" promptTitle="Playtest status" prompt="Playtest evidence for mechanical changes." type="list">
-      <formula1>"Not needed,Pending,Passed,Failed,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
